--- a/UploadFileData.xlsx
+++ b/UploadFileData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pradit.n\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\App Report\GJTH_InspecControl_New\GJTH_InspecControl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA63E92-8A37-424C-AF7D-D913122F0CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FF74F1-73CF-47AA-9E1B-670DE1A6ADA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CBBCBEB-C0D8-4BEB-AB85-3EB983E71CEF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>ItemID</t>
   </si>
@@ -113,25 +113,10 @@
     <t>InspecType</t>
   </si>
   <si>
-    <t>test0xxx</t>
-  </si>
-  <si>
-    <t>test002xx</t>
-  </si>
-  <si>
-    <t>test003xx</t>
-  </si>
-  <si>
-    <t>test004cc</t>
-  </si>
-  <si>
-    <t>test005ff</t>
-  </si>
-  <si>
-    <t>PO2602356</t>
-  </si>
-  <si>
-    <t>test0089</t>
+    <t>PO2603078</t>
+  </si>
+  <si>
+    <t>FIM/804/2026</t>
   </si>
 </sst>
 </file>
@@ -509,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA7D959-7A30-4507-91D7-BE7118E3D736}">
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
@@ -594,228 +579,32 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B2">
-        <v>613000400</v>
+        <v>503933002</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>0.54</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>0.54</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V2" t="s">
-        <v>26</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3">
-        <v>613000470</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3">
-        <v>6.86</v>
-      </c>
-      <c r="E3">
-        <v>6.86</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3" t="s">
-        <v>25</v>
-      </c>
-      <c r="V3" t="s">
-        <v>27</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4">
-        <v>613000700</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="E4">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4" t="s">
-        <v>26</v>
-      </c>
-      <c r="V4" t="s">
-        <v>28</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K5E5E5E Confidential</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{d0ebd98b-8037-439b-8d0f-46eeaff069ca}" enabled="1" method="Standard" siteId="{54cc0dd4-1f08-454f-8055-66227c421fb6}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>